--- a/Data/Hit_Location_Source.xlsx
+++ b/Data/Hit_Location_Source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\Stat_blocks\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E1ACD3-5449-459B-A1F8-96FF7A60F90C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9D558A-84E0-4E22-886B-C47117B4AAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="1425" windowWidth="30090" windowHeight="15345" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3075" yWindow="1620" windowWidth="32175" windowHeight="19260" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Humanoid" sheetId="1" r:id="rId1"/>
@@ -21,14 +21,16 @@
     <sheet name="Wyvern" sheetId="6" r:id="rId6"/>
     <sheet name="Harpy" sheetId="8" r:id="rId7"/>
     <sheet name="Lesser Hydra" sheetId="9" r:id="rId8"/>
-    <sheet name="Krashtkid" sheetId="10" r:id="rId11"/>
+    <sheet name="Krashtkid" sheetId="10" r:id="rId9"/>
+    <sheet name="Walktapus" sheetId="11" r:id="rId10"/>
+    <sheet name="Giant Honeybee" sheetId="12" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="152511" fullCalcOnLoad="1"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="99">
   <si>
     <t>Location</t>
   </si>
@@ -42,7 +44,7 @@
     <t>HP</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Cambria"/>
@@ -52,7 +54,7 @@
     </r>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Cambria"/>
@@ -62,7 +64,7 @@
     </r>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Cambria"/>
@@ -72,7 +74,7 @@
     </r>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Cambria"/>
@@ -82,7 +84,7 @@
     </r>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Cambria"/>
@@ -92,7 +94,7 @@
     </r>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Cambria"/>
@@ -102,7 +104,7 @@
     </r>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Cambria"/>
@@ -112,7 +114,7 @@
     </r>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Cambria"/>
@@ -122,7 +124,7 @@
     </r>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Cambria"/>
@@ -132,7 +134,7 @@
     </r>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Cambria"/>
@@ -142,7 +144,7 @@
     </r>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Cambria"/>
@@ -152,7 +154,7 @@
     </r>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Cambria"/>
@@ -162,7 +164,7 @@
     </r>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Cambria"/>
@@ -262,10 +264,7 @@
     <t>19–20</t>
   </si>
   <si>
-    <t>AP</t>
-  </si>
-  <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Cambria"/>
@@ -278,7 +277,7 @@
     <t>Right Center Leg</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Cambria"/>
@@ -288,7 +287,7 @@
     </r>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Cambria"/>
@@ -298,7 +297,7 @@
     </r>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Cambria"/>
@@ -308,7 +307,7 @@
     </r>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Cambria"/>
@@ -318,7 +317,7 @@
     </r>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Cambria"/>
@@ -328,7 +327,7 @@
     </r>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Cambria"/>
@@ -338,7 +337,7 @@
     </r>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Cambria"/>
@@ -348,7 +347,7 @@
     </r>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Cambria"/>
@@ -358,7 +357,7 @@
     </r>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="Cambria"/>
@@ -447,6 +446,48 @@
   </si>
   <si>
     <t>19-20</t>
+  </si>
+  <si>
+    <t>07-08</t>
+  </si>
+  <si>
+    <t>09-10</t>
+  </si>
+  <si>
+    <t>Tentacle 1</t>
+  </si>
+  <si>
+    <t>Tentacle 2</t>
+  </si>
+  <si>
+    <t>Tentacle 3</t>
+  </si>
+  <si>
+    <t>Tentacle 4</t>
+  </si>
+  <si>
+    <t>Tentacle 5</t>
+  </si>
+  <si>
+    <t>Tentacle 6</t>
+  </si>
+  <si>
+    <t>Tentacle 7</t>
+  </si>
+  <si>
+    <t>Tentacle 8</t>
+  </si>
+  <si>
+    <t>Left Center Leg</t>
+  </si>
+  <si>
+    <t>05-08</t>
+  </si>
+  <si>
+    <t>11-12</t>
+  </si>
+  <si>
+    <t>17-18</t>
   </si>
 </sst>
 </file>
@@ -457,7 +498,7 @@
     <numFmt numFmtId="164" formatCode="###0;###0"/>
     <numFmt numFmtId="165" formatCode="###00;###00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -578,62 +619,62 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="20">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="4" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="5" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="5" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="5" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="4" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="6" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -939,7 +980,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA69EDD2-C27B-4ECC-8321-332E2A93EF1B}">
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -948,7 +989,7 @@
     <col min="3" max="3" width="15.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -962,7 +1003,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="17.1" customHeight="1">
+    <row r="2" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -972,11 +1013,11 @@
       <c r="C2" s="3">
         <v>0</v>
       </c>
-      <c r="D2" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" ht="17.1" customHeight="1">
+      <c r="D2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -986,11 +1027,11 @@
       <c r="C3" s="3">
         <v>0</v>
       </c>
-      <c r="D3" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" ht="17.1" customHeight="1">
+      <c r="D3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1000,11 +1041,11 @@
       <c r="C4" s="3">
         <v>0</v>
       </c>
-      <c r="D4" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" ht="17.1" customHeight="1">
+      <c r="D4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -1014,11 +1055,11 @@
       <c r="C5" s="3">
         <v>0</v>
       </c>
-      <c r="D5" s="0">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" ht="17.1" customHeight="1">
+      <c r="D5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,11 +1069,11 @@
       <c r="C6" s="3">
         <v>0</v>
       </c>
-      <c r="D6" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" ht="17.1" customHeight="1">
+      <c r="D6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -1042,11 +1083,11 @@
       <c r="C7" s="3">
         <v>0</v>
       </c>
-      <c r="D7" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
+      <c r="D7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -1056,145 +1097,434 @@
       <c r="C8" s="3">
         <v>0</v>
       </c>
-      <c r="D8" s="0">
+      <c r="D8">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25095357-7E39-463F-9259-5BAF0281D033}">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8">
+        <v>11</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9">
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10">
+        <v>13</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11">
+        <v>14</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12">
+        <v>15</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13">
+        <v>16</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14">
+        <v>17</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15">
+        <v>18</v>
+      </c>
+      <c r="C15">
+        <v>4</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+      <c r="D16">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="0">
-        <v>3</v>
-      </c>
-      <c r="D2" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="0">
-        <v>3</v>
-      </c>
-      <c r="D3" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" s="0">
-        <v>3</v>
-      </c>
-      <c r="D4" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" s="0">
-        <v>3</v>
-      </c>
-      <c r="D5" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="0">
-        <v>3</v>
-      </c>
-      <c r="D6" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
+      <c r="B10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="0">
-        <v>3</v>
-      </c>
-      <c r="D7" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" s="0">
-        <v>7</v>
-      </c>
-      <c r="D8" s="0">
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{773C9D1F-34B4-483F-9672-DC7BE41640AD}">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="15.33203125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" ht="15">
+    <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1208,7 +1538,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
         <v>17</v>
       </c>
@@ -1218,11 +1548,11 @@
       <c r="C2" s="15">
         <v>8</v>
       </c>
-      <c r="D2" s="0">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="D2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>19</v>
       </c>
@@ -1232,11 +1562,11 @@
       <c r="C3" s="16">
         <v>4</v>
       </c>
-      <c r="D3" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="D3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>21</v>
       </c>
@@ -1246,22 +1576,21 @@
       <c r="C4" s="11">
         <v>4</v>
       </c>
-      <c r="D4" s="0">
+      <c r="D4">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC51D1B8-CB74-408C-815E-2124CEAE82DD}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="15.33203125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" ht="15">
+    <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1275,7 +1604,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
         <v>17</v>
       </c>
@@ -1285,11 +1614,11 @@
       <c r="C2" s="15">
         <v>8</v>
       </c>
-      <c r="D2" s="0">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="D2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>19</v>
       </c>
@@ -1299,11 +1628,11 @@
       <c r="C3" s="16">
         <v>4</v>
       </c>
-      <c r="D3" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="D3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>24</v>
       </c>
@@ -1313,32 +1642,31 @@
       <c r="C4" s="11">
         <v>4</v>
       </c>
-      <c r="D4" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
+      <c r="D4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="0">
-        <v>4</v>
-      </c>
-      <c r="D5" s="0">
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1735802-E1B3-41F4-8B26-633F7ADBBB5D}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1346,7 +1674,7 @@
     <col min="3" max="3" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15">
+    <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1360,7 +1688,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
@@ -1374,7 +1702,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>29</v>
       </c>
@@ -1388,7 +1716,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>30</v>
       </c>
@@ -1402,7 +1730,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>32</v>
       </c>
@@ -1416,7 +1744,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>33</v>
       </c>
@@ -1430,7 +1758,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
@@ -1444,7 +1772,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>36</v>
       </c>
@@ -1458,7 +1786,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>38</v>
       </c>
@@ -1472,7 +1800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>40</v>
       </c>
@@ -1486,7 +1814,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>42</v>
       </c>
@@ -1500,7 +1828,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>44</v>
       </c>
@@ -1514,7 +1842,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -1530,16 +1858,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5A134AC-5AFE-40C3-BD04-5D0E8BCBDCE8}">
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="15.5" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1547,15 +1874,15 @@
         <v>1</v>
       </c>
       <c r="C1" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="B2" s="18">
         <v>1</v>
@@ -1567,9 +1894,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1">
+    <row r="3" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B3" s="18">
         <v>2</v>
@@ -1581,24 +1908,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="18">
+        <v>3</v>
+      </c>
+      <c r="C4" s="18">
+        <v>6</v>
+      </c>
+      <c r="D4" s="19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="18">
-        <v>3</v>
-      </c>
-      <c r="C4" s="18">
-        <v>6</v>
-      </c>
-      <c r="D4" s="19">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="B5" s="18">
         <v>4</v>
       </c>
@@ -1609,7 +1936,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -1623,12 +1950,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="C7" s="18">
         <v>6</v>
@@ -1637,27 +1964,27 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="18">
+        <v>6</v>
+      </c>
+      <c r="D8" s="19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="18">
-        <v>6</v>
-      </c>
-      <c r="D8" s="19">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="C9" s="18">
         <v>6</v>
       </c>
@@ -1665,12 +1992,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C10" s="18">
         <v>6</v>
@@ -1681,319 +2008,437 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41FE66E0-0FAD-40EF-81E2-D4C3872DC248}">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="0">
+      <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" s="0">
-        <v>6</v>
-      </c>
-      <c r="D2" s="0">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+      <c r="C2">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="0">
-        <v>6</v>
-      </c>
-      <c r="D3" s="0">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
+      <c r="B4" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="0">
-        <v>6</v>
-      </c>
-      <c r="D4" s="0">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
+      <c r="B5" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="0">
-        <v>6</v>
-      </c>
-      <c r="D5" s="0">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="0" t="s">
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="0">
-        <v>6</v>
-      </c>
-      <c r="D6" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
+      <c r="B7" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="0">
-        <v>6</v>
-      </c>
-      <c r="D7" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="s">
+      <c r="B8" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="0">
-        <v>6</v>
-      </c>
-      <c r="D8" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="s">
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="0">
-        <v>6</v>
-      </c>
-      <c r="D9" s="0">
+      <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32B4C724-7179-41F4-BFDA-3DF7B6CCC900}">
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="B2" s="0" t="s">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="0">
+      <c r="C3">
         <v>1</v>
       </c>
-      <c r="D2" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+      <c r="D3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="0">
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="D3" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="0">
+      <c r="D5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6">
         <v>1</v>
       </c>
-      <c r="D4" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="0">
+      <c r="D6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="D5" s="0">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="0">
+      <c r="D7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8">
         <v>1</v>
       </c>
-      <c r="D6" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="0">
-        <v>1</v>
-      </c>
-      <c r="D7" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" s="0">
-        <v>1</v>
-      </c>
-      <c r="D8" s="0">
+      <c r="D8">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A64B2207-F483-4D23-86E8-410EED5160AA}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" s="0">
-        <v>6</v>
-      </c>
-      <c r="D2" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+      <c r="B3" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" s="0">
-        <v>6</v>
-      </c>
-      <c r="D3" s="0">
+      <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{367F79C5-63A6-4570-8177-61042BBF7290}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>